--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-related-person.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="370">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -198,13 +198,209 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>RelatedPerson.implicitRules</t>
+    <t>RelatedPerson.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>RelatedPerson.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -215,9 +411,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>RelatedPerson.language</t>
@@ -300,38 +493,10 @@
     <t>RelatedPerson.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>RelatedPerson.modifierExtension</t>
@@ -485,39 +650,16 @@
     <t>RelatedPerson.relationship.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>RelatedPerson.relationship:RolePerson.extension</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>RelatedPerson.relationship:RolePerson.coding</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -1324,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM50"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.84375" customWidth="true" bestFit="true"/>
@@ -1350,8 +1492,8 @@
     <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="9.6640625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="67.9296875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
@@ -1364,7 +1506,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="89.0078125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="16.3984375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="56.63671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1718,10 +1860,10 @@
         <v>35</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>60</v>
@@ -1732,9 +1874,7 @@
       <c r="M4" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>63</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>35</v>
@@ -1783,7 +1923,7 @@
         <v>35</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>36</v>
@@ -1792,13 +1932,13 @@
         <v>44</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>35</v>
@@ -1809,21 +1949,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>35</v>
@@ -1870,28 +2010,28 @@
         <v>35</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>74</v>
@@ -1900,16 +2040,16 @@
         <v>36</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>35</v>
@@ -1920,14 +2060,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1943,19 +2083,19 @@
         <v>35</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2005,7 +2145,7 @@
         <v>35</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>36</v>
@@ -2020,7 +2160,7 @@
         <v>57</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>35</v>
@@ -2031,21 +2171,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>35</v>
@@ -2054,19 +2194,19 @@
         <v>35</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2116,22 +2256,22 @@
         <v>35</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>35</v>
@@ -2142,21 +2282,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>35</v>
@@ -2165,19 +2305,19 @@
         <v>35</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2215,34 +2355,34 @@
         <v>35</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>35</v>
@@ -2253,14 +2393,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2273,26 +2413,24 @@
         <v>35</v>
       </c>
       <c r="I9" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J9" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="J9" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="K9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>35</v>
       </c>
@@ -2328,19 +2466,19 @@
         <v>35</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -2352,10 +2490,10 @@
         <v>56</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>35</v>
@@ -2366,18 +2504,20 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>44</v>
@@ -2392,18 +2532,18 @@
         <v>45</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>35</v>
       </c>
@@ -2412,7 +2552,7 @@
         <v>35</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>35</v>
@@ -2451,7 +2591,7 @@
         <v>35</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -2466,21 +2606,21 @@
         <v>57</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>113</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2491,38 +2631,34 @@
         <v>36</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q11" t="s" s="2">
-        <v>120</v>
-      </c>
+      <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
         <v>35</v>
       </c>
@@ -2542,13 +2678,13 @@
         <v>35</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>35</v>
@@ -2566,13 +2702,13 @@
         <v>35</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>56</v>
@@ -2581,21 +2717,21 @@
         <v>57</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>35</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2603,10 +2739,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>35</v>
@@ -2618,20 +2754,18 @@
         <v>45</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>35</v>
       </c>
@@ -2655,13 +2789,13 @@
         <v>35</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>35</v>
@@ -2679,36 +2813,36 @@
         <v>35</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2716,35 +2850,33 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="H13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>35</v>
       </c>
@@ -2768,35 +2900,37 @@
         <v>35</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>56</v>
@@ -2805,25 +2939,23 @@
         <v>57</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>142</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>35</v>
       </c>
@@ -2841,23 +2973,21 @@
         <v>35</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>35</v>
       </c>
@@ -2881,11 +3011,13 @@
         <v>35</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>35</v>
@@ -2903,13 +3035,13 @@
         <v>35</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>56</v>
@@ -2918,25 +3050,25 @@
         <v>57</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>142</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2955,15 +3087,17 @@
         <v>35</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>35</v>
@@ -3012,7 +3146,7 @@
         <v>35</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
@@ -3021,13 +3155,13 @@
         <v>44</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>35</v>
@@ -3038,14 +3172,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3064,16 +3198,16 @@
         <v>35</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3111,19 +3245,19 @@
         <v>35</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
@@ -3132,10 +3266,10 @@
         <v>37</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>58</v>
@@ -3149,14 +3283,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3172,23 +3306,21 @@
         <v>35</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>160</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>35</v>
       </c>
@@ -3224,19 +3356,19 @@
         <v>35</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
@@ -3248,56 +3380,60 @@
         <v>56</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>166</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>35</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>35</v>
       </c>
@@ -3333,34 +3469,34 @@
         <v>35</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>35</v>
@@ -3371,21 +3507,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>35</v>
@@ -3394,21 +3530,21 @@
         <v>35</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>35</v>
       </c>
@@ -3444,19 +3580,19 @@
         <v>35</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
@@ -3468,24 +3604,24 @@
         <v>56</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>35</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3493,7 +3629,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>44</v>
@@ -3502,35 +3638,37 @@
         <v>35</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="P20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q20" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="P20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
         <v>35</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>177</v>
+        <v>35</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>35</v>
@@ -3569,7 +3707,7 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
@@ -3584,21 +3722,21 @@
         <v>57</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>180</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3606,7 +3744,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>44</v>
@@ -3621,18 +3759,20 @@
         <v>45</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>35</v>
       </c>
@@ -3680,10 +3820,10 @@
         <v>35</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>44</v>
@@ -3692,24 +3832,24 @@
         <v>56</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3717,10 +3857,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>35</v>
@@ -3732,19 +3872,19 @@
         <v>45</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>35</v>
@@ -3769,37 +3909,35 @@
         <v>35</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>56</v>
@@ -3808,23 +3946,25 @@
         <v>57</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>35</v>
       </c>
@@ -3845,19 +3985,19 @@
         <v>45</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>35</v>
@@ -3882,13 +4022,11 @@
         <v>35</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>35</v>
+        <v>199</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>35</v>
@@ -3906,13 +4044,13 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>56</v>
@@ -3921,21 +4059,21 @@
         <v>57</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3955,23 +4093,19 @@
         <v>35</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>208</v>
+        <v>61</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>35</v>
       </c>
@@ -4019,7 +4153,7 @@
         <v>35</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -4028,38 +4162,38 @@
         <v>44</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>213</v>
+        <v>64</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>214</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>35</v>
@@ -4068,23 +4202,21 @@
         <v>35</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>217</v>
+        <v>68</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>218</v>
+        <v>69</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>35</v>
       </c>
@@ -4120,58 +4252,54 @@
         <v>35</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>221</v>
+        <v>74</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>223</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="E26" t="s" s="2">
-        <v>225</v>
-      </c>
+      <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>36</v>
       </c>
@@ -4188,19 +4316,19 @@
         <v>45</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>35</v>
@@ -4225,11 +4353,13 @@
         <v>35</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>227</v>
+        <v>35</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>35</v>
@@ -4247,7 +4377,7 @@
         <v>35</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>132</v>
+        <v>210</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -4262,21 +4392,21 @@
         <v>57</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>140</v>
+        <v>211</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>142</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4299,13 +4429,13 @@
         <v>35</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4356,7 +4486,7 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -4371,7 +4501,7 @@
         <v>35</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>35</v>
@@ -4382,14 +4512,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4408,16 +4538,16 @@
         <v>35</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4455,19 +4585,19 @@
         <v>35</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -4479,7 +4609,7 @@
         <v>56</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>58</v>
@@ -4493,10 +4623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4504,10 +4634,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>35</v>
@@ -4519,19 +4649,19 @@
         <v>45</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>35</v>
@@ -4541,7 +4671,7 @@
         <v>35</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>35</v>
+        <v>223</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>35</v>
@@ -4580,13 +4710,13 @@
         <v>35</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>56</v>
@@ -4595,21 +4725,21 @@
         <v>57</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>166</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4629,18 +4759,20 @@
         <v>35</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>35</v>
@@ -4689,7 +4821,7 @@
         <v>35</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -4698,38 +4830,38 @@
         <v>44</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>65</v>
+        <v>233</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>35</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>170</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>35</v>
@@ -4738,21 +4870,23 @@
         <v>35</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>93</v>
+        <v>237</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>35</v>
       </c>
@@ -4788,48 +4922,48 @@
         <v>35</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>156</v>
+        <v>241</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>35</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4837,7 +4971,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>44</v>
@@ -4855,16 +4989,16 @@
         <v>60</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>175</v>
+        <v>239</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>35</v>
@@ -4874,7 +5008,7 @@
         <v>35</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>234</v>
+        <v>35</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>35</v>
@@ -4913,7 +5047,7 @@
         <v>35</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
@@ -4928,21 +5062,21 @@
         <v>57</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>179</v>
+        <v>250</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>180</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>182</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4965,18 +5099,20 @@
         <v>45</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>183</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>35</v>
       </c>
@@ -5024,7 +5160,7 @@
         <v>35</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -5039,21 +5175,21 @@
         <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>188</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>190</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5076,19 +5212,19 @@
         <v>45</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>191</v>
+        <v>263</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>192</v>
+        <v>264</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>193</v>
+        <v>265</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>194</v>
+        <v>266</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>35</v>
@@ -5137,7 +5273,7 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>195</v>
+        <v>267</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -5152,32 +5288,36 @@
         <v>57</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>197</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>28</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="F35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>35</v>
@@ -5189,19 +5329,19 @@
         <v>45</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>35</v>
@@ -5226,13 +5366,11 @@
         <v>35</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>35</v>
+        <v>273</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>35</v>
@@ -5250,13 +5388,13 @@
         <v>35</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>56</v>
@@ -5265,21 +5403,21 @@
         <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5299,23 +5437,19 @@
         <v>35</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>208</v>
+        <v>61</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>35</v>
       </c>
@@ -5363,7 +5497,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -5372,38 +5506,38 @@
         <v>44</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>213</v>
+        <v>64</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>214</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>35</v>
@@ -5412,23 +5546,21 @@
         <v>35</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>217</v>
+        <v>68</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>218</v>
+        <v>69</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>35</v>
       </c>
@@ -5464,48 +5596,48 @@
         <v>35</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>221</v>
+        <v>74</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>223</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5525,22 +5657,22 @@
         <v>35</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>35</v>
@@ -5589,7 +5721,7 @@
         <v>35</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -5604,21 +5736,21 @@
         <v>57</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>247</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5629,7 +5761,7 @@
         <v>36</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>35</v>
@@ -5641,20 +5773,16 @@
         <v>35</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>249</v>
+        <v>60</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>35</v>
       </c>
@@ -5702,47 +5830,47 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>254</v>
+        <v>35</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>255</v>
+        <v>64</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>256</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>35</v>
@@ -5751,23 +5879,21 @@
         <v>35</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>67</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>258</v>
+        <v>68</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>259</v>
+        <v>69</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>35</v>
       </c>
@@ -5791,60 +5917,60 @@
         <v>35</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>261</v>
+        <v>35</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>262</v>
+        <v>35</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>263</v>
+        <v>35</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>257</v>
+        <v>74</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>264</v>
+        <v>58</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>265</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5852,7 +5978,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>44</v>
@@ -5867,16 +5993,20 @@
         <v>45</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>267</v>
+        <v>88</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>35</v>
       </c>
@@ -5885,7 +6015,7 @@
         <v>35</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>35</v>
+        <v>280</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>35</v>
@@ -5924,7 +6054,7 @@
         <v>35</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -5939,21 +6069,21 @@
         <v>57</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>35</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5964,7 +6094,7 @@
         <v>36</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>35</v>
@@ -5973,23 +6103,21 @@
         <v>35</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>272</v>
+        <v>60</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>35</v>
       </c>
@@ -6037,13 +6165,13 @@
         <v>35</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>56</v>
@@ -6052,21 +6180,21 @@
         <v>57</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>278</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>279</v>
+        <v>236</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6077,7 +6205,7 @@
         <v>36</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>35</v>
@@ -6086,22 +6214,22 @@
         <v>35</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>280</v>
+        <v>128</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>35</v>
@@ -6150,36 +6278,36 @@
         <v>35</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>279</v>
+        <v>241</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>285</v>
+        <v>57</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>287</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6199,21 +6327,23 @@
         <v>35</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>289</v>
+        <v>60</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>35</v>
       </c>
@@ -6261,7 +6391,7 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6273,24 +6403,24 @@
         <v>56</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>293</v>
+        <v>57</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>294</v>
+        <v>250</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>295</v>
+        <v>35</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>296</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6301,7 +6431,7 @@
         <v>36</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>35</v>
@@ -6310,22 +6440,22 @@
         <v>35</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>298</v>
+        <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>35</v>
@@ -6374,13 +6504,13 @@
         <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>56</v>
@@ -6389,21 +6519,21 @@
         <v>57</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>35</v>
+        <v>260</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6423,19 +6553,23 @@
         <v>35</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>150</v>
+        <v>263</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>35</v>
       </c>
@@ -6483,7 +6617,7 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -6492,31 +6626,31 @@
         <v>44</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>65</v>
+        <v>268</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>35</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6535,18 +6669,20 @@
         <v>35</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>92</v>
+        <v>287</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>93</v>
+        <v>288</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>155</v>
+        <v>289</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>35</v>
       </c>
@@ -6582,19 +6718,19 @@
         <v>35</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>156</v>
+        <v>286</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -6606,28 +6742,28 @@
         <v>56</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>58</v>
+        <v>292</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>35</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>307</v>
+        <v>35</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6640,25 +6776,25 @@
         <v>35</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>92</v>
+        <v>295</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>95</v>
+        <v>298</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>35</v>
@@ -6707,7 +6843,7 @@
         <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -6719,24 +6855,24 @@
         <v>56</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>58</v>
+        <v>301</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>35</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6744,7 +6880,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>44</v>
@@ -6756,22 +6892,22 @@
         <v>35</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>314</v>
+        <v>239</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>35</v>
@@ -6796,13 +6932,13 @@
         <v>35</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>71</v>
+        <v>307</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>72</v>
+        <v>308</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>73</v>
+        <v>309</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>35</v>
@@ -6820,10 +6956,10 @@
         <v>35</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>44</v>
@@ -6835,21 +6971,21 @@
         <v>57</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6869,23 +7005,19 @@
         <v>35</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>115</v>
+        <v>313</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>35</v>
       </c>
@@ -6933,7 +7065,7 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -6948,12 +7080,1021 @@
         <v>57</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK51" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AL51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>35</v>
       </c>
     </row>
